--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="722" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{755A1F68-695C-4642-A205-205EF8B9A370}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>

--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationloisir/Shared Documents/Prestations Loisirs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="722" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{755A1F68-695C-4642-A205-205EF8B9A370}"/>
+  <xr:revisionPtr revIDLastSave="725" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDEABA51-8094-4B9B-AE95-93012165D1D1}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,9 +116,6 @@
     <t>Lemaitre Morgand</t>
   </si>
   <si>
-    <t>Liegeois Joell</t>
-  </si>
-  <si>
     <t>Moscato Victor</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
   </si>
   <si>
     <t>Duruisseau Antoine</t>
+  </si>
+  <si>
+    <t>Liégeois Joell</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>[1]DEKLERCK!$F$2</f>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1">
         <f>[1]KINIF!$F$2</f>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>[1]LABBE!$F$2</f>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>[1]LIEGEOIS!$F$2</f>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>[1]MOSCATO!$F$2</f>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1">
         <f>[1]NEZER!$F$2</f>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>[1]PESESSE!$F$2</f>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>[1]SEGHIAR!$F$2</f>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1">
         <f>[1]SUSAM!$F$2</f>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="str">
         <f>[1]TIBEAU!$F$2</f>
@@ -2405,25 +2405,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a6b1418315c503125b81deceb3e14f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db3d71b0-92fa-400b-b303-110676c7e1a6" xmlns:ns3="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b9cfce4172cb86f233e713e45f29f51c" ns2:_="" ns3:_="">
     <xsd:import namespace="db3d71b0-92fa-400b-b303-110676c7e1a6"/>
@@ -2634,25 +2615,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A27A95-3717-46C0-8F53-2FF09BECAD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2669,4 +2651,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationloisir/Shared Documents/Prestations Loisirs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="725" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDEABA51-8094-4B9B-AE95-93012165D1D1}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D5F4F4-C75C-4A35-84FF-B1A82B873F94}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" r:id="rId1"/>
+    <sheet name="2025" sheetId="2" r:id="rId1"/>
+    <sheet name="2026" sheetId="1" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
   <si>
     <t>Agent</t>
   </si>
@@ -201,7 +202,46 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="26">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[h]:mm"/>
     </dxf>
@@ -327,6 +367,71 @@
             <v>1.2900883838383841</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>2.3972222222222221</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.3222222222222224</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.9736111111111114</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.6104166666666671</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.4604166666666671</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.1034722222222224</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.2236111111111114</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.5888888888888892</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.5826388888888894</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.5326388888888893</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.8326388888888894</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.6715277777777784</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
@@ -364,6 +469,71 @@
             <v>2.1943313492063492</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.5583333333333331</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>1.7041666666666664</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.6930555555555553</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.1138888888888887</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.3638888888888887</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.7138888888888888</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.8131944444444443</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.7272083333333332</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.9272083333333332</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.8355416666666664</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.9417916666666664</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.9420694444444442</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="2">
@@ -401,6 +571,21 @@
             <v>0.61262626262626263</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.25</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.29166666666666663</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="2">
@@ -438,6 +623,71 @@
             <v>1.0923611111111113</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.15416666666666662</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.3027777777777777</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.0576388888888888</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.3076388888888888</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.5611111111111109</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.9791666666666667</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.2694444444444444</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.8916666666666666</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.7638888888888888</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.8569444444444443</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.9159722222222222</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.0090277777777779</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="5">
         <row r="2">
@@ -473,6 +723,51 @@
         <row r="10">
           <cell r="K10">
             <v>1.18</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.7361111111111105E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.49375000000000002</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.75</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.76041666666666663</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.87916666666666665</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.46805555555555556</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.71180555555555558</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.46666666666666667</v>
           </cell>
         </row>
       </sheetData>
@@ -513,6 +808,71 @@
             <v>0.88691589811155058</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.1305555555555555</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.7729166666666667</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.7554563492063493</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.78809523809523818</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.96865079365079376</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.1388888888888891</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.2326388888888891</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.322916666666667</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.4659722222222225</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.3807669082125607</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.97451690821256065</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.8849335748792273</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="2">
@@ -550,6 +910,71 @@
             <v>0.92280303030303013</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.56666666666666665</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.73333333333333339</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.64781746031746035</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.49295634920634923</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.6289682539682557E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.49791666666666662</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.69722222222222219</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.86458333333333326</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.70082070707070687</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.78055555555555556</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.90555555555555556</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.88472222222222219</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="5">
@@ -619,6 +1044,71 @@
             <v>-0.11901350461133056</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.54277777777777769</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.3726388888888888</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.76708333333333323</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.1101388888888888</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.1372222222222221</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.1916666666666667</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.2416666666666667</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.82500000000000007</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.72638888888888897</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.4766304347826088</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.37107487922705323</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>-4.350845410628007E-2</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="2">
@@ -656,6 +1146,71 @@
             <v>3.6867470765089894</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.4486111111111108</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.95972222222222192</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.4277777777777774</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.6847222222222218</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.0736111111111106</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.3347222222222226</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.4354166666666668</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.6854166666666668</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.7563131313131315</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.7046826965305231</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>2.7664882520860785</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.8838932228463121</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="12">
         <row r="2">
@@ -693,6 +1248,71 @@
             <v>0.29578678201743214</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.42152777777777778</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.40138888888888891</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.1805555555555625E-2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.50069444444444455</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>5.8333333333333459E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.21527777777777779</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.37986111111111109</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.54236111111111107</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.38604040404040402</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.2336792929292929</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.38256818181818181</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.33817490696438063</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="13">
         <row r="2">
@@ -730,6 +1350,71 @@
             <v>-0.68048269710595555</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.17569444444444446</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2.8472222222222232E-2</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.11656746031746033</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.13531746031746034</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.19087301587301592</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.26628472222222227</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.17825441919191926</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.24643497474747483</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.25825315656565662</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.29714204545454548</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.36214204545454548</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.10460549574694314</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
@@ -767,6 +1452,71 @@
             <v>2.1204575163398687</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1.3354166666666667</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>1.2902777777777779</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.3527777777777779</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>1.5555555555555556</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>1.6381944444444443</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>1.5583333333333333</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.5010227272727272</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.4633282828282828</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.5244393939393939</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.2536060606060604</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.3702727272727271</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.5560227272727272</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="15">
         <row r="2">
@@ -804,6 +1554,31 @@
             <v>0.36805555555555558</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.53749999999999998</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.53888888888888886</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.57847222222222228</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.27013888888888893</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="16">
         <row r="2">
@@ -841,6 +1616,71 @@
             <v>0.8603283148777161</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.32430555555555551</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.10069444444444436</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.72777777777777775</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.21299603174603168</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>-4.1170634920634969E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>5.9722222222222232E-2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.30972222222222223</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.53888888888888897</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.55574494949494957</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.60716403162055343</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.40438625384277571</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.34502952869657688</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="17">
         <row r="2">
@@ -876,6 +1716,71 @@
         <row r="10">
           <cell r="K10">
             <v>0.41508838383838398</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>8.333333333333337E-2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>7.6388888888888923E-2</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>7.6388888888888923E-2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.34375000000000011</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.15486111111111123</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.43472222222222223</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.60138888888888897</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.51597222222222228</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.32689393939393946</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.25328282828282833</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.28106060606060612</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.28106060606060612</v>
           </cell>
         </row>
       </sheetData>
@@ -916,6 +1821,71 @@
             <v>0.47029671717171739</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.23541666666666669</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.23541666666666669</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.23541666666666669</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.22083333333333335</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.46319444444444446</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.41388888888888897</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>0.53402777777777788</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>0.65416666666666679</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.77916666666666679</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.90416666666666679</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.0222222222222224</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>2.4305555555555802E-2</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="20">
         <row r="2">
@@ -953,6 +1923,71 @@
             <v>1.8787878787878791</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.85138888888888886</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.70416666666666661</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.59583333333333321</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.59583333333333321</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.39722222222222209</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.81388888888888888</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.151388888888889</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.615277777777778</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.3826388888888892</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.75902777777777808</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.94513888888888919</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.72569444444444475</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="21">
         <row r="2">
@@ -990,6 +2025,71 @@
             <v>2.283583333333334</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.89097222222222217</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.77986111111111101</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>1.5576388888888886</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.3895833333333329</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.2743055555555554</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.4763888888888888</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.3355277777777776</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.6126111111111108</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.7313611111111111</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.2424722222222222</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>2.0544166666666666</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>1.9002499999999998</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="22">
         <row r="2">
@@ -1027,6 +2127,71 @@
             <v>0.35779649644338701</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>0.1715277777777777</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>0.29652777777777772</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>0.25208333333333327</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>0.31041666666666662</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>0.22291666666666662</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>0.80486111111111114</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>1.5633055555555555</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>1.3348333333333333</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>1.3946818181818181</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>1.2726709486166008</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>1.0622542819499341</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.52286100709613292</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="23">
         <row r="2">
@@ -1062,6 +2227,21 @@
         <row r="10">
           <cell r="K10">
             <v>0.2203679653679653</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.23819444444444443</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.19722222222222219</v>
           </cell>
         </row>
       </sheetData>
@@ -1102,6 +2282,71 @@
             <v>2.2972222222222221</v>
           </cell>
         </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v xml:space="preserve"> </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>3.3777777777777782</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>3.6277777777777782</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="K24">
+            <v>2.1992063492063494</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="K25">
+            <v>2.3957341269841272</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="K26">
+            <v>2.4978174603174605</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="K27">
+            <v>2.9069444444444446</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="K28">
+            <v>2.0951388888888891</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="K29">
+            <v>2.3451388888888891</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>2.5590277777777781</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>2.8090277777777781</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>3.0208333333333335</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>3.2708333333333335</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="26">
         <row r="2">
@@ -1137,6 +2382,31 @@
         <row r="10">
           <cell r="K10">
             <v>-3.0303030303031608E-3</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="K30">
+            <v>0.25</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="K31">
+            <v>0.25347222222222221</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="K32">
+            <v>0.35069444444444442</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="K33">
+            <v>0.35486111111111107</v>
           </cell>
         </row>
       </sheetData>
@@ -1146,6 +2416,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D6F0F7A8-5DF8-4F28-BA32-D1E0A725B282}" name="Tableau13" displayName="Tableau13" ref="A1:N24" totalsRowShown="0">
+  <autoFilter ref="A1:N24" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N24">
+    <sortCondition ref="A1:A24"/>
+  </sortState>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{754EF1F6-D6CE-4B61-B059-689C5D9CEF25}" name="Agent"/>
+    <tableColumn id="2" xr3:uid="{2FD1CE32-ECE7-4893-8BC2-4006C2FCF160}" name="Solde 31/08" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{2E7CEC48-66C0-4270-8819-C5AEB96FCCE1}" name="Janvier" dataDxfId="11">
+      <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{0C9F15EC-B037-4437-BD2B-E7CF27699C3A}" name="Février" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{3C217D23-BDAC-4CD8-940B-C4CA82ECA661}" name="Mars" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{7B9C3F84-98FA-457E-AA2C-37B43CA891DE}" name="Avril" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{E9BBC20F-6E7D-483A-A2C4-C1ACB46104CD}" name="Mai" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{24F62277-DAE6-4829-B809-3E2D477715E4}" name="Juin" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{0670983D-E820-43B1-A435-DE806CC60452}" name="Juillet" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{0CDE416F-EB10-46CE-846C-6E62D241F509}" name="Août" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{CEF508F5-A8A9-4275-A501-618AF335963E}" name="Septembre" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{5A242AD9-4A28-46D7-9DC6-012058F6C4AC}" name="Octobre" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{039DCC9B-124D-4CDE-8FC1-EABB8CB091DC}" name="Novembre" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{406CB3AB-04B7-47C3-A699-F13C6891C693}" name="Décembre" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}" name="Tableau1" displayName="Tableau1" ref="A1:N24" totalsRowShown="0">
   <autoFilter ref="A1:N24" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N24">
@@ -1153,21 +2451,21 @@
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1435,6 +2733,1389 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40D9281-9BE8-4862-911C-4DD8AD138DB8}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>[1]BECKER!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C2" s="1">
+        <f>[1]BECKER!$K$22</f>
+        <v>2.3972222222222221</v>
+      </c>
+      <c r="D2" s="1">
+        <f>[1]BECKER!$K$23</f>
+        <v>2.3222222222222224</v>
+      </c>
+      <c r="E2" s="1">
+        <f>[1]BECKER!$K$24</f>
+        <v>2.9736111111111114</v>
+      </c>
+      <c r="F2" s="1">
+        <f>[1]BECKER!$K$25</f>
+        <v>2.6104166666666671</v>
+      </c>
+      <c r="G2" s="1">
+        <f>[1]BECKER!$K$26</f>
+        <v>2.4604166666666671</v>
+      </c>
+      <c r="H2" s="1">
+        <f>[1]BECKER!$K$27</f>
+        <v>2.1034722222222224</v>
+      </c>
+      <c r="I2" s="1">
+        <f>[1]BECKER!$K$28</f>
+        <v>2.2236111111111114</v>
+      </c>
+      <c r="J2" s="1">
+        <f>[1]BECKER!$K$29</f>
+        <v>1.5888888888888892</v>
+      </c>
+      <c r="K2" s="1">
+        <f>[1]BECKER!$K$30</f>
+        <v>1.5826388888888894</v>
+      </c>
+      <c r="L2" s="1">
+        <f>[1]BECKER!$K$31</f>
+        <v>1.5326388888888893</v>
+      </c>
+      <c r="M2" s="1">
+        <f>[1]BECKER!$K$32</f>
+        <v>1.8326388888888894</v>
+      </c>
+      <c r="N2" s="1">
+        <f>[1]BECKER!$K$33</f>
+        <v>1.6715277777777784</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>[1]BOUSSIFET!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C3" s="1">
+        <f>[1]BOUSSIFET!$K$22</f>
+        <v>1.5583333333333331</v>
+      </c>
+      <c r="D3" s="1">
+        <f>[1]BOUSSIFET!$K$23</f>
+        <v>1.7041666666666664</v>
+      </c>
+      <c r="E3" s="1">
+        <f>[1]BOUSSIFET!$K$24</f>
+        <v>1.6930555555555553</v>
+      </c>
+      <c r="F3" s="1">
+        <f>[1]BOUSSIFET!$K$25</f>
+        <v>1.1138888888888887</v>
+      </c>
+      <c r="G3" s="1">
+        <f>[1]BOUSSIFET!$K$26</f>
+        <v>1.3638888888888887</v>
+      </c>
+      <c r="H3" s="1">
+        <f>[1]BOUSSIFET!$K$27</f>
+        <v>1.7138888888888888</v>
+      </c>
+      <c r="I3" s="1">
+        <f>[1]BOUSSIFET!$K$28</f>
+        <v>1.8131944444444443</v>
+      </c>
+      <c r="J3" s="1">
+        <f>[1]BOUSSIFET!$K$29</f>
+        <v>1.7272083333333332</v>
+      </c>
+      <c r="K3" s="1">
+        <f>[1]BOUSSIFET!$K$30</f>
+        <v>1.9272083333333332</v>
+      </c>
+      <c r="L3" s="1">
+        <f>[1]BOUSSIFET!$K$31</f>
+        <v>1.8355416666666664</v>
+      </c>
+      <c r="M3" s="1">
+        <f>[1]BOUSSIFET!$K$32</f>
+        <v>1.9417916666666664</v>
+      </c>
+      <c r="N3" s="1">
+        <f>[1]BOUSSIFET!$K$33</f>
+        <v>1.9420694444444442</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1">
+        <f>[1]DEKLERCK!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <f>[1]DEKLERCK!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <f>[1]DEKLERCK!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <f>[1]DEKLERCK!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <f>[1]DEKLERCK!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <f>[1]DEKLERCK!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <f>[1]DEKLERCK!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <f>[1]DEKLERCK!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <f>[1]DEKLERCK!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <f>[1]DEKLERCK!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <f>[1]DEKLERCK!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <f>[1]DEKLERCK!$K$32</f>
+        <v>0.25</v>
+      </c>
+      <c r="N4" s="1">
+        <f>[1]DEKLERCK!$K$33</f>
+        <v>0.29166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>[1]DELFORGE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C5" s="1">
+        <f>[1]DELFORGE!$K$22</f>
+        <v>0.15416666666666662</v>
+      </c>
+      <c r="D5" s="1">
+        <f>[1]DELFORGE!$K$23</f>
+        <v>0.3027777777777777</v>
+      </c>
+      <c r="E5" s="1">
+        <f>[1]DELFORGE!$K$24</f>
+        <v>1.0576388888888888</v>
+      </c>
+      <c r="F5" s="1">
+        <f>[1]DELFORGE!$K$25</f>
+        <v>1.3076388888888888</v>
+      </c>
+      <c r="G5" s="1">
+        <f>[1]DELFORGE!$K$26</f>
+        <v>1.5611111111111109</v>
+      </c>
+      <c r="H5" s="1">
+        <f>[1]DELFORGE!$K$27</f>
+        <v>1.9791666666666667</v>
+      </c>
+      <c r="I5" s="1">
+        <f>[1]DELFORGE!$K$28</f>
+        <v>2.2694444444444444</v>
+      </c>
+      <c r="J5" s="1">
+        <f>[1]DELFORGE!$K$29</f>
+        <v>1.8916666666666666</v>
+      </c>
+      <c r="K5" s="1">
+        <f>[1]DELFORGE!$K$30</f>
+        <v>1.7638888888888888</v>
+      </c>
+      <c r="L5" s="1">
+        <f>[1]DELFORGE!$K$31</f>
+        <v>1.8569444444444443</v>
+      </c>
+      <c r="M5" s="1">
+        <f>[1]DELFORGE!$K$32</f>
+        <v>1.9159722222222222</v>
+      </c>
+      <c r="N5" s="1">
+        <f>[1]DELFORGE!$K$33</f>
+        <v>2.0090277777777779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>[1]DEWEZ!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C6" s="1">
+        <f>[1]DEWEZ!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <f>[1]DEWEZ!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <f>[1]DEWEZ!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <f>[1]DEWEZ!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <f>[1]DEWEZ!$K$26</f>
+        <v>1.7361111111111105E-2</v>
+      </c>
+      <c r="H6" s="1">
+        <f>[1]DEWEZ!$K$27</f>
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="I6" s="1">
+        <f>[1]DEWEZ!$K$28</f>
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="1">
+        <f>[1]DEWEZ!$K$29</f>
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="K6" s="1">
+        <f>[1]DEWEZ!$K$30</f>
+        <v>0.87916666666666665</v>
+      </c>
+      <c r="L6" s="1">
+        <f>[1]DEWEZ!$K$31</f>
+        <v>0.46805555555555556</v>
+      </c>
+      <c r="M6" s="1">
+        <f>[1]DEWEZ!$K$32</f>
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="N6" s="1">
+        <f>[1]DEWEZ!$K$33</f>
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>[1]DIRICK!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C7" s="1">
+        <f>[1]DIRICK!$K$22</f>
+        <v>1.1305555555555555</v>
+      </c>
+      <c r="D7" s="1">
+        <f>[1]DIRICK!$K$23</f>
+        <v>0.7729166666666667</v>
+      </c>
+      <c r="E7" s="1">
+        <f>[1]DIRICK!$K$24</f>
+        <v>0.7554563492063493</v>
+      </c>
+      <c r="F7" s="1">
+        <f>[1]DIRICK!$K$25</f>
+        <v>0.78809523809523818</v>
+      </c>
+      <c r="G7" s="1">
+        <f>[1]DIRICK!$K$26</f>
+        <v>0.96865079365079376</v>
+      </c>
+      <c r="H7" s="1">
+        <f>[1]DIRICK!$K$27</f>
+        <v>1.1388888888888891</v>
+      </c>
+      <c r="I7" s="1">
+        <f>[1]DIRICK!$K$28</f>
+        <v>1.2326388888888891</v>
+      </c>
+      <c r="J7" s="1">
+        <f>[1]DIRICK!$K$29</f>
+        <v>1.322916666666667</v>
+      </c>
+      <c r="K7" s="1">
+        <f>[1]DIRICK!$K$30</f>
+        <v>1.4659722222222225</v>
+      </c>
+      <c r="L7" s="1">
+        <f>[1]DIRICK!$K$31</f>
+        <v>1.3807669082125607</v>
+      </c>
+      <c r="M7" s="1">
+        <f>[1]DIRICK!$K$32</f>
+        <v>0.97451690821256065</v>
+      </c>
+      <c r="N7" s="1">
+        <f>[1]DIRICK!$K$33</f>
+        <v>0.8849335748792273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>[1]DUCHENE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C8" s="1">
+        <f>[1]DUCHENE!$K$22</f>
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="D8" s="1">
+        <f>[1]DUCHENE!$K$23</f>
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="E8" s="1">
+        <f>[1]DUCHENE!$K$24</f>
+        <v>0.64781746031746035</v>
+      </c>
+      <c r="F8" s="1">
+        <f>[1]DUCHENE!$K$25</f>
+        <v>0.49295634920634923</v>
+      </c>
+      <c r="G8" s="1">
+        <f>[1]DUCHENE!$K$26</f>
+        <v>2.6289682539682557E-2</v>
+      </c>
+      <c r="H8" s="1">
+        <f>[1]DUCHENE!$K$27</f>
+        <v>0.49791666666666662</v>
+      </c>
+      <c r="I8" s="1">
+        <f>[1]DUCHENE!$K$28</f>
+        <v>0.69722222222222219</v>
+      </c>
+      <c r="J8" s="1">
+        <f>[1]DUCHENE!$K$29</f>
+        <v>0.86458333333333326</v>
+      </c>
+      <c r="K8" s="1">
+        <f>[1]DUCHENE!$K$30</f>
+        <v>0.70082070707070687</v>
+      </c>
+      <c r="L8" s="1">
+        <f>[1]DUCHENE!$K$31</f>
+        <v>0.78055555555555556</v>
+      </c>
+      <c r="M8" s="1">
+        <f>[1]DUCHENE!$K$32</f>
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="N8" s="1">
+        <f>[1]DUCHENE!$K$33</f>
+        <v>0.88472222222222219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1">
+        <f>[1]DURUISSEAU!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <f>[1]DURUISSEAU!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <f>[1]DURUISSEAU!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <f>[1]DURUISSEAU!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <f>[1]DURUISSEAU!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <f>[1]DURUISSEAU!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <f>[1]DURUISSEAU!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <f>[1]DURUISSEAU!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <f>[1]DURUISSEAU!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <f>[1]DURUISSEAU!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <f>[1]DURUISSEAU!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <f>[1]DURUISSEAU!$K$32</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <f>[1]DURUISSEAU!$K$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>[1]HEIRBRANT!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C10" s="1">
+        <f>[1]HEIRBRANT!$K$22</f>
+        <v>0.54277777777777769</v>
+      </c>
+      <c r="D10" s="1">
+        <f>[1]HEIRBRANT!$K$23</f>
+        <v>0.3726388888888888</v>
+      </c>
+      <c r="E10" s="1">
+        <f>[1]HEIRBRANT!$K$24</f>
+        <v>0.76708333333333323</v>
+      </c>
+      <c r="F10" s="1">
+        <f>[1]HEIRBRANT!$K$25</f>
+        <v>1.1101388888888888</v>
+      </c>
+      <c r="G10" s="1">
+        <f>[1]HEIRBRANT!$K$26</f>
+        <v>1.1372222222222221</v>
+      </c>
+      <c r="H10" s="1">
+        <f>[1]HEIRBRANT!$K$27</f>
+        <v>1.1916666666666667</v>
+      </c>
+      <c r="I10" s="1">
+        <f>[1]HEIRBRANT!$K$28</f>
+        <v>1.2416666666666667</v>
+      </c>
+      <c r="J10" s="1">
+        <f>[1]HEIRBRANT!$K$29</f>
+        <v>0.82500000000000007</v>
+      </c>
+      <c r="K10" s="1">
+        <f>[1]HEIRBRANT!$K$30</f>
+        <v>0.72638888888888897</v>
+      </c>
+      <c r="L10" s="1">
+        <f>[1]HEIRBRANT!$K$31</f>
+        <v>0.4766304347826088</v>
+      </c>
+      <c r="M10" s="1">
+        <f>[1]HEIRBRANT!$K$32</f>
+        <v>0.37107487922705323</v>
+      </c>
+      <c r="N10" s="1">
+        <f>[1]HEIRBRANT!$K$33</f>
+        <v>-4.350845410628007E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>[1]INZERILLI!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C11" s="1">
+        <f>[1]INZERILLI!$K$22</f>
+        <v>1.4486111111111108</v>
+      </c>
+      <c r="D11" s="1">
+        <f>[1]INZERILLI!$K$23</f>
+        <v>0.95972222222222192</v>
+      </c>
+      <c r="E11" s="1">
+        <f>[1]INZERILLI!$K$24</f>
+        <v>1.4277777777777774</v>
+      </c>
+      <c r="F11" s="1">
+        <f>[1]INZERILLI!$K$25</f>
+        <v>1.6847222222222218</v>
+      </c>
+      <c r="G11" s="1">
+        <f>[1]INZERILLI!$K$26</f>
+        <v>2.0736111111111106</v>
+      </c>
+      <c r="H11" s="1">
+        <f>[1]INZERILLI!$K$27</f>
+        <v>2.3347222222222226</v>
+      </c>
+      <c r="I11" s="1">
+        <f>[1]INZERILLI!$K$28</f>
+        <v>2.4354166666666668</v>
+      </c>
+      <c r="J11" s="1">
+        <f>[1]INZERILLI!$K$29</f>
+        <v>2.6854166666666668</v>
+      </c>
+      <c r="K11" s="1">
+        <f>[1]INZERILLI!$K$30</f>
+        <v>2.7563131313131315</v>
+      </c>
+      <c r="L11" s="1">
+        <f>[1]INZERILLI!$K$31</f>
+        <v>2.7046826965305231</v>
+      </c>
+      <c r="M11" s="1">
+        <f>[1]INZERILLI!$K$32</f>
+        <v>2.7664882520860785</v>
+      </c>
+      <c r="N11" s="1">
+        <f>[1]INZERILLI!$K$33</f>
+        <v>2.8838932228463121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>[1]JAMAR!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C12" s="1">
+        <f>[1]JAMAR!$K$22</f>
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="D12" s="1">
+        <f>[1]JAMAR!$K$23</f>
+        <v>0.40138888888888891</v>
+      </c>
+      <c r="E12" s="1">
+        <f>[1]JAMAR!$K$24</f>
+        <v>1.1805555555555625E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <f>[1]JAMAR!$K$25</f>
+        <v>0.50069444444444455</v>
+      </c>
+      <c r="G12" s="1">
+        <f>[1]JAMAR!$K$26</f>
+        <v>5.8333333333333459E-2</v>
+      </c>
+      <c r="H12" s="1">
+        <f>[1]JAMAR!$K$27</f>
+        <v>0.21527777777777779</v>
+      </c>
+      <c r="I12" s="1">
+        <f>[1]JAMAR!$K$28</f>
+        <v>0.37986111111111109</v>
+      </c>
+      <c r="J12" s="1">
+        <f>[1]JAMAR!$K$29</f>
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="K12" s="1">
+        <f>[1]JAMAR!$K$30</f>
+        <v>0.38604040404040402</v>
+      </c>
+      <c r="L12" s="1">
+        <f>[1]JAMAR!$K$31</f>
+        <v>0.2336792929292929</v>
+      </c>
+      <c r="M12" s="1">
+        <f>[1]JAMAR!$K$32</f>
+        <v>0.38256818181818181</v>
+      </c>
+      <c r="N12" s="1">
+        <f>[1]JAMAR!$K$33</f>
+        <v>0.33817490696438063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <f>[1]JAMART!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C13" s="1">
+        <f>[1]JAMART!$K$22</f>
+        <v>0.17569444444444446</v>
+      </c>
+      <c r="D13" s="1">
+        <f>[1]JAMART!$K$23</f>
+        <v>2.8472222222222232E-2</v>
+      </c>
+      <c r="E13" s="1">
+        <f>[1]JAMART!$K$24</f>
+        <v>0.11656746031746033</v>
+      </c>
+      <c r="F13" s="1">
+        <f>[1]JAMART!$K$25</f>
+        <v>0.13531746031746034</v>
+      </c>
+      <c r="G13" s="1">
+        <f>[1]JAMART!$K$26</f>
+        <v>0.19087301587301592</v>
+      </c>
+      <c r="H13" s="1">
+        <f>[1]JAMART!$K$27</f>
+        <v>0.26628472222222227</v>
+      </c>
+      <c r="I13" s="1">
+        <f>[1]JAMART!$K$28</f>
+        <v>0.17825441919191926</v>
+      </c>
+      <c r="J13" s="1">
+        <f>[1]JAMART!$K$29</f>
+        <v>0.24643497474747483</v>
+      </c>
+      <c r="K13" s="1">
+        <f>[1]JAMART!$K$30</f>
+        <v>0.25825315656565662</v>
+      </c>
+      <c r="L13" s="1">
+        <f>[1]JAMART!$K$31</f>
+        <v>0.29714204545454548</v>
+      </c>
+      <c r="M13" s="1">
+        <f>[1]JAMART!$K$32</f>
+        <v>0.36214204545454548</v>
+      </c>
+      <c r="N13" s="1">
+        <f>[1]JAMART!$K$33</f>
+        <v>0.10460549574694314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>[1]KINIF!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C14" s="1">
+        <f>[1]KINIF!$K$22</f>
+        <v>1.3354166666666667</v>
+      </c>
+      <c r="D14" s="1">
+        <f>[1]KINIF!$K$23</f>
+        <v>1.2902777777777779</v>
+      </c>
+      <c r="E14" s="1">
+        <f>[1]KINIF!$K$24</f>
+        <v>1.3527777777777779</v>
+      </c>
+      <c r="F14" s="1">
+        <f>[1]KINIF!$K$25</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="G14" s="1">
+        <f>[1]KINIF!$K$26</f>
+        <v>1.6381944444444443</v>
+      </c>
+      <c r="H14" s="1">
+        <f>[1]KINIF!$K$27</f>
+        <v>1.5583333333333333</v>
+      </c>
+      <c r="I14" s="1">
+        <f>[1]KINIF!$K$28</f>
+        <v>1.5010227272727272</v>
+      </c>
+      <c r="J14" s="1">
+        <f>[1]KINIF!$K$29</f>
+        <v>1.4633282828282828</v>
+      </c>
+      <c r="K14" s="1">
+        <f>[1]KINIF!$K$30</f>
+        <v>1.5244393939393939</v>
+      </c>
+      <c r="L14" s="1">
+        <f>[1]KINIF!$K$31</f>
+        <v>1.2536060606060604</v>
+      </c>
+      <c r="M14" s="1">
+        <f>[1]KINIF!$K$32</f>
+        <v>1.3702727272727271</v>
+      </c>
+      <c r="N14" s="1">
+        <f>[1]KINIF!$K$33</f>
+        <v>1.5560227272727272</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1">
+        <f>[1]LABBE!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <f>[1]LABBE!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <f>[1]LABBE!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <f>[1]LABBE!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <f>[1]LABBE!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <f>[1]LABBE!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <f>[1]LABBE!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <f>[1]LABBE!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <f>[1]LABBE!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <f>[1]LABBE!$K$30</f>
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="L15" s="1">
+        <f>[1]LABBE!$K$31</f>
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="M15" s="1">
+        <f>[1]LABBE!$K$32</f>
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="N15" s="1">
+        <f>[1]LABBE!$K$33</f>
+        <v>0.27013888888888893</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <f>[1]LAMBERT!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C16" s="1">
+        <f>[1]LAMBERT!$K$22</f>
+        <v>0.32430555555555551</v>
+      </c>
+      <c r="D16" s="1">
+        <f>[1]LAMBERT!$K$23</f>
+        <v>0.10069444444444436</v>
+      </c>
+      <c r="E16" s="1">
+        <f>[1]LAMBERT!$K$24</f>
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="F16" s="1">
+        <f>[1]LAMBERT!$K$25</f>
+        <v>0.21299603174603168</v>
+      </c>
+      <c r="G16" s="1">
+        <f>[1]LAMBERT!$K$26</f>
+        <v>-4.1170634920634969E-2</v>
+      </c>
+      <c r="H16" s="1">
+        <f>[1]LAMBERT!$K$27</f>
+        <v>5.9722222222222232E-2</v>
+      </c>
+      <c r="I16" s="1">
+        <f>[1]LAMBERT!$K$28</f>
+        <v>0.30972222222222223</v>
+      </c>
+      <c r="J16" s="1">
+        <f>[1]LAMBERT!$K$29</f>
+        <v>0.53888888888888897</v>
+      </c>
+      <c r="K16" s="1">
+        <f>[1]LAMBERT!$K$30</f>
+        <v>0.55574494949494957</v>
+      </c>
+      <c r="L16" s="1">
+        <f>[1]LAMBERT!$K$31</f>
+        <v>0.60716403162055343</v>
+      </c>
+      <c r="M16" s="1">
+        <f>[1]LAMBERT!$K$32</f>
+        <v>0.40438625384277571</v>
+      </c>
+      <c r="N16" s="1">
+        <f>[1]LAMBERT!$K$33</f>
+        <v>0.34502952869657688</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <f>[1]LEMAITRE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C17" s="1">
+        <f>[1]LEMAITRE!$K$22</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="D17" s="1">
+        <f>[1]LEMAITRE!$K$23</f>
+        <v>7.6388888888888923E-2</v>
+      </c>
+      <c r="E17" s="1">
+        <f>[1]LEMAITRE!$K$24</f>
+        <v>7.6388888888888923E-2</v>
+      </c>
+      <c r="F17" s="1">
+        <f>[1]LEMAITRE!$K$25</f>
+        <v>0.34375000000000011</v>
+      </c>
+      <c r="G17" s="1">
+        <f>[1]LEMAITRE!$K$26</f>
+        <v>0.15486111111111123</v>
+      </c>
+      <c r="H17" s="1">
+        <f>[1]LEMAITRE!$K$27</f>
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="I17" s="1">
+        <f>[1]LEMAITRE!$K$28</f>
+        <v>0.60138888888888897</v>
+      </c>
+      <c r="J17" s="1">
+        <f>[1]LEMAITRE!$K$29</f>
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="K17" s="1">
+        <f>[1]LEMAITRE!$K$30</f>
+        <v>0.32689393939393946</v>
+      </c>
+      <c r="L17" s="1">
+        <f>[1]LEMAITRE!$K$31</f>
+        <v>0.25328282828282833</v>
+      </c>
+      <c r="M17" s="1">
+        <f>[1]LEMAITRE!$K$32</f>
+        <v>0.28106060606060612</v>
+      </c>
+      <c r="N17" s="1">
+        <f>[1]LEMAITRE!$K$33</f>
+        <v>0.28106060606060612</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <f>[1]LIEGEOIS!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C18" s="1">
+        <f>[1]LIEGEOIS!$K$22</f>
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="D18" s="1">
+        <f>[1]LIEGEOIS!$K$23</f>
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="E18" s="1">
+        <f>[1]LIEGEOIS!$K$24</f>
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="F18" s="1">
+        <f>[1]LIEGEOIS!$K$25</f>
+        <v>0.22083333333333335</v>
+      </c>
+      <c r="G18" s="1">
+        <f>[1]LIEGEOIS!$K$26</f>
+        <v>0.46319444444444446</v>
+      </c>
+      <c r="H18" s="1">
+        <f>[1]LIEGEOIS!$K$27</f>
+        <v>0.41388888888888897</v>
+      </c>
+      <c r="I18" s="1">
+        <f>[1]LIEGEOIS!$K$28</f>
+        <v>0.53402777777777788</v>
+      </c>
+      <c r="J18" s="1">
+        <f>[1]LIEGEOIS!$K$29</f>
+        <v>0.65416666666666679</v>
+      </c>
+      <c r="K18" s="1">
+        <f>[1]LIEGEOIS!$K$30</f>
+        <v>0.77916666666666679</v>
+      </c>
+      <c r="L18" s="1">
+        <f>[1]LIEGEOIS!$K$31</f>
+        <v>0.90416666666666679</v>
+      </c>
+      <c r="M18" s="1">
+        <f>[1]LIEGEOIS!$K$32</f>
+        <v>1.0222222222222224</v>
+      </c>
+      <c r="N18" s="1">
+        <f>[1]LIEGEOIS!$K$33</f>
+        <v>2.4305555555555802E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <f>[1]MOSCATO!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C19" s="1">
+        <f>[1]MOSCATO!$K$22</f>
+        <v>0.85138888888888886</v>
+      </c>
+      <c r="D19" s="1">
+        <f>[1]MOSCATO!$K$23</f>
+        <v>0.70416666666666661</v>
+      </c>
+      <c r="E19" s="1">
+        <f>[1]MOSCATO!$K$24</f>
+        <v>0.59583333333333321</v>
+      </c>
+      <c r="F19" s="1">
+        <f>[1]MOSCATO!$K$25</f>
+        <v>0.59583333333333321</v>
+      </c>
+      <c r="G19" s="1">
+        <f>[1]MOSCATO!$K$26</f>
+        <v>0.39722222222222209</v>
+      </c>
+      <c r="H19" s="1">
+        <f>[1]MOSCATO!$K$27</f>
+        <v>0.81388888888888888</v>
+      </c>
+      <c r="I19" s="1">
+        <f>[1]MOSCATO!$K$28</f>
+        <v>1.151388888888889</v>
+      </c>
+      <c r="J19" s="1">
+        <f>[1]MOSCATO!$K$29</f>
+        <v>1.615277777777778</v>
+      </c>
+      <c r="K19" s="1">
+        <f>[1]MOSCATO!$K$30</f>
+        <v>1.3826388888888892</v>
+      </c>
+      <c r="L19" s="1">
+        <f>[1]MOSCATO!$K$31</f>
+        <v>0.75902777777777808</v>
+      </c>
+      <c r="M19" s="1">
+        <f>[1]MOSCATO!$K$32</f>
+        <v>0.94513888888888919</v>
+      </c>
+      <c r="N19" s="1">
+        <f>[1]MOSCATO!$K$33</f>
+        <v>0.72569444444444475</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <f>[1]NEZER!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C20" s="1">
+        <f>[1]NEZER!$K$22</f>
+        <v>0.89097222222222217</v>
+      </c>
+      <c r="D20" s="1">
+        <f>[1]NEZER!$K$23</f>
+        <v>0.77986111111111101</v>
+      </c>
+      <c r="E20" s="1">
+        <f>[1]NEZER!$K$24</f>
+        <v>1.5576388888888886</v>
+      </c>
+      <c r="F20" s="1">
+        <f>[1]NEZER!$K$25</f>
+        <v>2.3895833333333329</v>
+      </c>
+      <c r="G20" s="1">
+        <f>[1]NEZER!$K$26</f>
+        <v>2.2743055555555554</v>
+      </c>
+      <c r="H20" s="1">
+        <f>[1]NEZER!$K$27</f>
+        <v>2.4763888888888888</v>
+      </c>
+      <c r="I20" s="1">
+        <f>[1]NEZER!$K$28</f>
+        <v>2.3355277777777776</v>
+      </c>
+      <c r="J20" s="1">
+        <f>[1]NEZER!$K$29</f>
+        <v>2.6126111111111108</v>
+      </c>
+      <c r="K20" s="1">
+        <f>[1]NEZER!$K$30</f>
+        <v>2.7313611111111111</v>
+      </c>
+      <c r="L20" s="1">
+        <f>[1]NEZER!$K$31</f>
+        <v>2.2424722222222222</v>
+      </c>
+      <c r="M20" s="1">
+        <f>[1]NEZER!$K$32</f>
+        <v>2.0544166666666666</v>
+      </c>
+      <c r="N20" s="1">
+        <f>[1]NEZER!$K$33</f>
+        <v>1.9002499999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>[1]PESESSE!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C21" s="1">
+        <f>[1]PESESSE!$K$22</f>
+        <v>0.1715277777777777</v>
+      </c>
+      <c r="D21" s="1">
+        <f>[1]PESESSE!$K$23</f>
+        <v>0.29652777777777772</v>
+      </c>
+      <c r="E21" s="1">
+        <f>[1]PESESSE!$K$24</f>
+        <v>0.25208333333333327</v>
+      </c>
+      <c r="F21" s="1">
+        <f>[1]PESESSE!$K$25</f>
+        <v>0.31041666666666662</v>
+      </c>
+      <c r="G21" s="1">
+        <f>[1]PESESSE!$K$26</f>
+        <v>0.22291666666666662</v>
+      </c>
+      <c r="H21" s="1">
+        <f>[1]PESESSE!$K$27</f>
+        <v>0.80486111111111114</v>
+      </c>
+      <c r="I21" s="1">
+        <f>[1]PESESSE!$K$28</f>
+        <v>1.5633055555555555</v>
+      </c>
+      <c r="J21" s="1">
+        <f>[1]PESESSE!$K$29</f>
+        <v>1.3348333333333333</v>
+      </c>
+      <c r="K21" s="1">
+        <f>[1]PESESSE!$K$30</f>
+        <v>1.3946818181818181</v>
+      </c>
+      <c r="L21" s="1">
+        <f>[1]PESESSE!$K$31</f>
+        <v>1.2726709486166008</v>
+      </c>
+      <c r="M21" s="1">
+        <f>[1]PESESSE!$K$32</f>
+        <v>1.0622542819499341</v>
+      </c>
+      <c r="N21" s="1">
+        <f>[1]PESESSE!$K$33</f>
+        <v>0.52286100709613292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1">
+        <f>[1]SEGHIAR!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <f>[1]SEGHIAR!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <f>[1]SEGHIAR!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <f>[1]SEGHIAR!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <f>[1]SEGHIAR!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <f>[1]SEGHIAR!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <f>[1]SEGHIAR!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <f>[1]SEGHIAR!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <f>[1]SEGHIAR!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <f>[1]SEGHIAR!$K$30</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <f>[1]SEGHIAR!$K$31</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <f>[1]SEGHIAR!$K$32</f>
+        <v>0.23819444444444443</v>
+      </c>
+      <c r="N22" s="1">
+        <f>[1]SEGHIAR!$K$33</f>
+        <v>0.19722222222222219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <f>[1]SUSAM!$E$19</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C23" s="1">
+        <f>[1]SUSAM!$K$22</f>
+        <v>3.3777777777777782</v>
+      </c>
+      <c r="D23" s="1">
+        <f>[1]SUSAM!$K$23</f>
+        <v>3.6277777777777782</v>
+      </c>
+      <c r="E23" s="1">
+        <f>[1]SUSAM!$K$24</f>
+        <v>2.1992063492063494</v>
+      </c>
+      <c r="F23" s="1">
+        <f>[1]SUSAM!$K$25</f>
+        <v>2.3957341269841272</v>
+      </c>
+      <c r="G23" s="1">
+        <f>[1]SUSAM!$K$26</f>
+        <v>2.4978174603174605</v>
+      </c>
+      <c r="H23" s="1">
+        <f>[1]SUSAM!$K$27</f>
+        <v>2.9069444444444446</v>
+      </c>
+      <c r="I23" s="1">
+        <f>[1]SUSAM!$K$28</f>
+        <v>2.0951388888888891</v>
+      </c>
+      <c r="J23" s="1">
+        <f>[1]SUSAM!$K$29</f>
+        <v>2.3451388888888891</v>
+      </c>
+      <c r="K23" s="1">
+        <f>[1]SUSAM!$K$30</f>
+        <v>2.5590277777777781</v>
+      </c>
+      <c r="L23" s="1">
+        <f>[1]SUSAM!$K$31</f>
+        <v>2.8090277777777781</v>
+      </c>
+      <c r="M23" s="1">
+        <f>[1]SUSAM!$K$32</f>
+        <v>3.0208333333333335</v>
+      </c>
+      <c r="N23" s="1">
+        <f>[1]SUSAM!$K$33</f>
+        <v>3.2708333333333335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1">
+        <f>[1]TIBEAU!$E$19</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <f>[1]TIBEAU!$K$22</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <f>[1]TIBEAU!$K$23</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <f>[1]TIBEAU!$K$24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <f>[1]TIBEAU!$K$25</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <f>[1]TIBEAU!$K$26</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <f>[1]TIBEAU!$K$27</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <f>[1]TIBEAU!$K$28</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <f>[1]TIBEAU!$K$29</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <f>[1]TIBEAU!$K$30</f>
+        <v>0.25</v>
+      </c>
+      <c r="L24" s="1">
+        <f>[1]TIBEAU!$K$31</f>
+        <v>0.25347222222222221</v>
+      </c>
+      <c r="M24" s="1">
+        <f>[1]TIBEAU!$K$32</f>
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="N24" s="1">
+        <f>[1]TIBEAU!$K$33</f>
+        <v>0.35486111111111107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationloisir/Shared Documents/Prestations Loisirs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D5F4F4-C75C-4A35-84FF-B1A82B873F94}"/>
+  <xr:revisionPtr revIDLastSave="774" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA941E8-9070-4013-AC02-332B88EC6F08}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>Agent</t>
   </si>
@@ -299,6 +299,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ANCART"/>
@@ -367,6 +368,11 @@
             <v>1.2900883838383841</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.135227272727273</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -436,7 +442,7 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="F2">
-            <v>1.0295694444444441</v>
+            <v>0.75734722222222195</v>
           </cell>
         </row>
         <row r="5">
@@ -467,6 +473,11 @@
         <row r="10">
           <cell r="K10">
             <v>2.1943313492063492</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>2.1221091269841272</v>
           </cell>
         </row>
         <row r="19">
@@ -568,7 +579,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.61262626262626263</v>
+            <v>0.62455808080808073</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.70511363636363633</v>
           </cell>
         </row>
         <row r="19">
@@ -623,6 +639,11 @@
             <v>1.0923611111111113</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.245138888888889</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -725,6 +746,11 @@
             <v>1.18</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.1397222222222223</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -771,43 +797,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7">
-        <row r="2">
-          <cell r="F2" t="str">
-            <v xml:space="preserve"> </v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>0.85437801932367174</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>0.71410024154589391</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="K7">
-            <v>0.57937801932367172</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="K8">
-            <v>0.60243357487922733</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="K9">
-            <v>0.81285024154589403</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="K10">
-            <v>0.88691589811155058</v>
-          </cell>
-        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -887,27 +878,32 @@
         </row>
         <row r="6">
           <cell r="K6">
-            <v>1.1673611111111111</v>
+            <v>1.179861111111111</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>1.1256944444444443</v>
+            <v>1.1381944444444443</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>0.92652777777777762</v>
+            <v>0.93902777777777757</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>1.0640277777777776</v>
+            <v>1.0765277777777775</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.92280303030303013</v>
+            <v>0.93530303030303008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.1443308080808079</v>
           </cell>
         </row>
         <row r="19">
@@ -1004,7 +1000,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-6.1319073083779013E-2</v>
+            <v>-3.8844325609031533E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>4.379456327985734E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -1026,22 +1027,27 @@
         </row>
         <row r="7">
           <cell r="K7">
-            <v>0.21621376811594217</v>
+            <v>1.0495471014492757</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>1.899154589371993E-2</v>
+            <v>0.85232487922705347</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>-3.4480676328502269E-2</v>
+            <v>0.79954710144927565</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-0.11901350461133056</v>
+            <v>0.89468599033816454</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.2953804347826088</v>
           </cell>
         </row>
         <row r="19">
@@ -1113,7 +1119,7 @@
       <sheetData sheetId="11">
         <row r="2">
           <cell r="F2">
-            <v>1.5026432228463118</v>
+            <v>1.2248654450685339</v>
           </cell>
         </row>
         <row r="5">
@@ -1144,6 +1150,11 @@
         <row r="10">
           <cell r="K10">
             <v>3.6867470765089894</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>3.6589692987312117</v>
           </cell>
         </row>
         <row r="19">
@@ -1245,7 +1256,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.29578678201743214</v>
+            <v>0.31933223656288667</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.4440147762454264</v>
           </cell>
         </row>
         <row r="19">
@@ -1347,7 +1363,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-0.68048269710595555</v>
+            <v>-0.55687158599484443</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>-0.44929222091547927</v>
           </cell>
         </row>
         <row r="19">
@@ -1419,7 +1440,7 @@
       <sheetData sheetId="14">
         <row r="2">
           <cell r="F2">
-            <v>1.0969949494949494</v>
+            <v>0.38935606060606043</v>
           </cell>
         </row>
         <row r="5">
@@ -1450,6 +1471,11 @@
         <row r="10">
           <cell r="K10">
             <v>2.1204575163398687</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.6128186274509797</v>
           </cell>
         </row>
         <row r="19">
@@ -1554,6 +1580,11 @@
             <v>0.36805555555555558</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.33640873015873018</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -1588,32 +1619,37 @@
         </row>
         <row r="5">
           <cell r="K5">
-            <v>0.53252952869657688</v>
+            <v>0.54502952869657695</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>0.15544619536324361</v>
+            <v>0.37766841758546582</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>1.0096128620299103</v>
+            <v>1.2318350842521326</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>1.0468152429822912</v>
+            <v>1.2690374652045135</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>1.1256060926554938</v>
+            <v>1.362093020760069</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.8603283148777161</v>
+            <v>1.2565374652045134</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.4433430207600688</v>
           </cell>
         </row>
         <row r="19">
@@ -1718,6 +1754,11 @@
             <v>0.41508838383838398</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.35883838383838396</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1784,7 +1825,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="18" refreshError="1"/>
       <sheetData sheetId="19">
         <row r="2">
           <cell r="F2" t="str">
@@ -1798,27 +1839,32 @@
         </row>
         <row r="6">
           <cell r="K6">
-            <v>0.11736111111111136</v>
+            <v>0.12361111111111137</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>0.17651515151515176</v>
+            <v>0.19469696969696995</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>0.2785984848484851</v>
+            <v>0.29678030303030328</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>0.4035984848484851</v>
+            <v>0.42178030303030328</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.47029671717171739</v>
+            <v>0.49416035353535381</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.5219381313131316</v>
           </cell>
         </row>
         <row r="19">
@@ -1920,7 +1966,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>1.8787878787878791</v>
+            <v>1.8895833333333336</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>2.0402777777777779</v>
           </cell>
         </row>
         <row r="19">
@@ -1991,8 +2042,8 @@
       </sheetData>
       <sheetData sheetId="21">
         <row r="2">
-          <cell r="F2">
-            <v>7.8888888888886122E-3</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -2023,6 +2074,11 @@
         <row r="10">
           <cell r="K10">
             <v>2.283583333333334</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.8676111111111118</v>
           </cell>
         </row>
         <row r="19">
@@ -2127,6 +2183,11 @@
             <v>0.35779649644338701</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.40868935358624414</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2229,6 +2290,11 @@
             <v>0.2203679653679653</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="K11">
+            <v>0.2203679653679653</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -2245,11 +2311,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="24" refreshError="1"/>
       <sheetData sheetId="25">
         <row r="2">
-          <cell r="F2">
-            <v>0.65000000000000036</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -2279,7 +2345,12 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>2.2972222222222221</v>
+            <v>2.3562500000000002</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>1.6562500000000002</v>
           </cell>
         </row>
         <row r="19">
@@ -2382,6 +2453,11 @@
         <row r="10">
           <cell r="K10">
             <v>-3.0303030303031608E-3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>-7.1969696969698127E-3</v>
           </cell>
         </row>
         <row r="19">
@@ -2423,49 +2499,49 @@
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{754EF1F6-D6CE-4B61-B059-689C5D9CEF25}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{2FD1CE32-ECE7-4893-8BC2-4006C2FCF160}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{2E7CEC48-66C0-4270-8819-C5AEB96FCCE1}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{2FD1CE32-ECE7-4893-8BC2-4006C2FCF160}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{2E7CEC48-66C0-4270-8819-C5AEB96FCCE1}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0C9F15EC-B037-4437-BD2B-E7CF27699C3A}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{3C217D23-BDAC-4CD8-940B-C4CA82ECA661}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{7B9C3F84-98FA-457E-AA2C-37B43CA891DE}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{E9BBC20F-6E7D-483A-A2C4-C1ACB46104CD}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{24F62277-DAE6-4829-B809-3E2D477715E4}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{0670983D-E820-43B1-A435-DE806CC60452}" name="Juillet" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{0CDE416F-EB10-46CE-846C-6E62D241F509}" name="Août" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{CEF508F5-A8A9-4275-A501-618AF335963E}" name="Septembre" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{5A242AD9-4A28-46D7-9DC6-012058F6C4AC}" name="Octobre" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{039DCC9B-124D-4CDE-8FC1-EABB8CB091DC}" name="Novembre" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{406CB3AB-04B7-47C3-A699-F13C6891C693}" name="Décembre" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{0C9F15EC-B037-4437-BD2B-E7CF27699C3A}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{3C217D23-BDAC-4CD8-940B-C4CA82ECA661}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{7B9C3F84-98FA-457E-AA2C-37B43CA891DE}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{E9BBC20F-6E7D-483A-A2C4-C1ACB46104CD}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{24F62277-DAE6-4829-B809-3E2D477715E4}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{0670983D-E820-43B1-A435-DE806CC60452}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{0CDE416F-EB10-46CE-846C-6E62D241F509}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{CEF508F5-A8A9-4275-A501-618AF335963E}" name="Septembre" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{5A242AD9-4A28-46D7-9DC6-012058F6C4AC}" name="Octobre" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{039DCC9B-124D-4CDE-8FC1-EABB8CB091DC}" name="Novembre" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{406CB3AB-04B7-47C3-A699-F13C6891C693}" name="Décembre" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}" name="Tableau1" displayName="Tableau1" ref="A1:N24" totalsRowShown="0">
-  <autoFilter ref="A1:N24" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N24">
-    <sortCondition ref="A1:A24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}" name="Tableau1" displayName="Tableau1" ref="A1:N23" totalsRowShown="0">
+  <autoFilter ref="A1:N23" xr:uid="{C7300799-99B8-4EB6-AE56-6C90EDB091F8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N23">
+    <sortCondition ref="A1:A23"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
       <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4117,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -4211,7 +4287,10 @@
         <f>[1]BECKER!$K$10</f>
         <v>1.2900883838383841</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <f>[1]BECKER!$K$11</f>
+        <v>1.135227272727273</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -4224,7 +4303,7 @@
       </c>
       <c r="B3" s="1">
         <f>[1]BOUSSIFET!$F$2</f>
-        <v>1.0295694444444441</v>
+        <v>0.75734722222222195</v>
       </c>
       <c r="C3" s="1">
         <f>[1]BOUSSIFET!$K$5</f>
@@ -4250,7 +4329,10 @@
         <f>[1]BOUSSIFET!$K$10</f>
         <v>2.1943313492063492</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <f>[1]BOUSSIFET!$K$11</f>
+        <v>2.1221091269841272</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4287,9 +4369,12 @@
       </c>
       <c r="H4" s="1">
         <f>[1]DEKLERCK!$K$10</f>
-        <v>0.61262626262626263</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>0.62455808080808073</v>
+      </c>
+      <c r="I4" s="1">
+        <f>[1]DEKLERCK!$K$11</f>
+        <v>0.70511363636363633</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -4328,7 +4413,10 @@
         <f>[1]DELFORGE!$K$10</f>
         <v>1.0923611111111113</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <f>[1]DELFORGE!$K$11</f>
+        <v>1.245138888888889</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -4367,7 +4455,10 @@
         <f>[1]DEWEZ!$K$10</f>
         <v>1.18</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <f>[1]DEWEZ!$K$11</f>
+        <v>1.1397222222222223</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -4376,37 +4467,40 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>[1]DIRICK!$F$2</f>
+        <f>[1]DUCHENE!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C7" s="1">
-        <f>[1]DIRICK!$K$5</f>
-        <v>0.85437801932367174</v>
+        <f>[1]DUCHENE!$K$5</f>
+        <v>0.94236111111111109</v>
       </c>
       <c r="D7" s="1">
-        <f>[1]DIRICK!$K$6</f>
-        <v>0.71410024154589391</v>
+        <f>[1]DUCHENE!$K$6</f>
+        <v>1.179861111111111</v>
       </c>
       <c r="E7" s="1">
-        <f>[1]DIRICK!$K$7</f>
-        <v>0.57937801932367172</v>
+        <f>[1]DUCHENE!$K$7</f>
+        <v>1.1381944444444443</v>
       </c>
       <c r="F7" s="1">
-        <f>[1]DIRICK!$K$8</f>
-        <v>0.60243357487922733</v>
+        <f>[1]DUCHENE!$K$8</f>
+        <v>0.93902777777777757</v>
       </c>
       <c r="G7" s="1">
-        <f>[1]DIRICK!$K$9</f>
-        <v>0.81285024154589403</v>
+        <f>[1]DUCHENE!$K$9</f>
+        <v>1.0765277777777775</v>
       </c>
       <c r="H7" s="1">
-        <f>[1]DIRICK!$K$10</f>
-        <v>0.88691589811155058</v>
-      </c>
-      <c r="I7" s="1"/>
+        <f>[1]DUCHENE!$K$10</f>
+        <v>0.93530303030303008</v>
+      </c>
+      <c r="I7" s="1">
+        <f>[1]DUCHENE!$K$11</f>
+        <v>1.1443308080808079</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -4415,37 +4509,37 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="str">
-        <f>[1]DUCHENE!$F$2</f>
-        <v xml:space="preserve"> </v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="1"/>
       <c r="C8" s="1">
-        <f>[1]DUCHENE!$K$5</f>
-        <v>0.94236111111111109</v>
+        <f>[1]DURUISSEAU!$K$5</f>
+        <v>0.25</v>
       </c>
       <c r="D8" s="1">
-        <f>[1]DUCHENE!$K$6</f>
-        <v>1.1673611111111111</v>
+        <f>[1]DURUISSEAU!$K$6</f>
+        <v>0.25486111111111109</v>
       </c>
       <c r="E8" s="1">
-        <f>[1]DUCHENE!$K$7</f>
-        <v>1.1256944444444443</v>
+        <f>[1]DURUISSEAU!$K$7</f>
+        <v>0.20555555555555555</v>
       </c>
       <c r="F8" s="1">
-        <f>[1]DUCHENE!$K$8</f>
-        <v>0.92652777777777762</v>
+        <f>[1]DURUISSEAU!$K$8</f>
+        <v>0.2472222222222222</v>
       </c>
       <c r="G8" s="1">
-        <f>[1]DUCHENE!$K$9</f>
-        <v>1.0640277777777776</v>
+        <f>[1]DURUISSEAU!$K$9</f>
+        <v>0.22005718954248363</v>
       </c>
       <c r="H8" s="1">
-        <f>[1]DUCHENE!$K$10</f>
-        <v>0.92280303030303013</v>
-      </c>
-      <c r="I8" s="1"/>
+        <f>[1]DURUISSEAU!$K$10</f>
+        <v>-3.8844325609031533E-2</v>
+      </c>
+      <c r="I8" s="1">
+        <f>[1]DURUISSEAU!$K$11</f>
+        <v>4.379456327985734E-2</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -4454,34 +4548,40 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>[1]HEIRBRANT!$F$2</f>
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="C9" s="1">
-        <f>[1]DURUISSEAU!$K$5</f>
-        <v>0.25</v>
+        <f>[1]HEIRBRANT!$K$5</f>
+        <v>0.27732487922705329</v>
       </c>
       <c r="D9" s="1">
-        <f>[1]DURUISSEAU!$K$6</f>
-        <v>0.25486111111111109</v>
+        <f>[1]HEIRBRANT!$K$6</f>
+        <v>0.31968599033816442</v>
       </c>
       <c r="E9" s="1">
-        <f>[1]DURUISSEAU!$K$7</f>
-        <v>0.20555555555555555</v>
+        <f>[1]HEIRBRANT!$K$7</f>
+        <v>1.0495471014492757</v>
       </c>
       <c r="F9" s="1">
-        <f>[1]DURUISSEAU!$K$8</f>
-        <v>0.2472222222222222</v>
+        <f>[1]HEIRBRANT!$K$8</f>
+        <v>0.85232487922705347</v>
       </c>
       <c r="G9" s="1">
-        <f>[1]DURUISSEAU!$K$9</f>
-        <v>0.22005718954248363</v>
+        <f>[1]HEIRBRANT!$K$9</f>
+        <v>0.79954710144927565</v>
       </c>
       <c r="H9" s="1">
-        <f>[1]DURUISSEAU!$K$10</f>
-        <v>-6.1319073083779013E-2</v>
-      </c>
-      <c r="I9" s="1"/>
+        <f>[1]HEIRBRANT!$K$10</f>
+        <v>0.89468599033816454</v>
+      </c>
+      <c r="I9" s="1">
+        <f>[1]HEIRBRANT!$K$11</f>
+        <v>1.2953804347826088</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -4490,37 +4590,40 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="str">
-        <f>[1]HEIRBRANT!$F$2</f>
-        <v xml:space="preserve"> </v>
+        <v>20</v>
+      </c>
+      <c r="B10" s="1">
+        <f>[1]INZERILLI!$F$2</f>
+        <v>1.2248654450685339</v>
       </c>
       <c r="C10" s="1">
-        <f>[1]HEIRBRANT!$K$5</f>
-        <v>0.27732487922705329</v>
+        <f>[1]INZERILLI!$K$5</f>
+        <v>2.92417100062409</v>
       </c>
       <c r="D10" s="1">
-        <f>[1]HEIRBRANT!$K$6</f>
-        <v>0.31968599033816442</v>
+        <f>[1]INZERILLI!$K$6</f>
+        <v>2.9991710006240897</v>
       </c>
       <c r="E10" s="1">
-        <f>[1]HEIRBRANT!$K$7</f>
-        <v>0.21621376811594217</v>
+        <f>[1]INZERILLI!$K$7</f>
+        <v>3.8811785763816657</v>
       </c>
       <c r="F10" s="1">
-        <f>[1]HEIRBRANT!$K$8</f>
-        <v>1.899154589371993E-2</v>
+        <f>[1]INZERILLI!$K$8</f>
+        <v>3.5562182589213482</v>
       </c>
       <c r="G10" s="1">
-        <f>[1]HEIRBRANT!$K$9</f>
-        <v>-3.4480676328502269E-2</v>
+        <f>[1]INZERILLI!$K$9</f>
+        <v>3.6214061674180802</v>
       </c>
       <c r="H10" s="1">
-        <f>[1]HEIRBRANT!$K$10</f>
-        <v>-0.11901350461133056</v>
-      </c>
-      <c r="I10" s="1"/>
+        <f>[1]INZERILLI!$K$10</f>
+        <v>3.6867470765089894</v>
+      </c>
+      <c r="I10" s="1">
+        <f>[1]INZERILLI!$K$11</f>
+        <v>3.6589692987312117</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -4529,37 +4632,40 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <f>[1]INZERILLI!$F$2</f>
-        <v>1.5026432228463118</v>
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>[1]JAMAR!$F$2</f>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C11" s="1">
-        <f>[1]INZERILLI!$K$5</f>
-        <v>2.92417100062409</v>
+        <f>[1]JAMAR!$K$5</f>
+        <v>0.45900824029771398</v>
       </c>
       <c r="D11" s="1">
-        <f>[1]INZERILLI!$K$6</f>
-        <v>2.9991710006240897</v>
+        <f>[1]JAMAR!$K$6</f>
+        <v>0.50275824029771399</v>
       </c>
       <c r="E11" s="1">
-        <f>[1]INZERILLI!$K$7</f>
-        <v>3.8811785763816657</v>
+        <f>[1]JAMAR!$K$7</f>
+        <v>0.83470268474215836</v>
       </c>
       <c r="F11" s="1">
-        <f>[1]INZERILLI!$K$8</f>
-        <v>3.5562182589213482</v>
+        <f>[1]JAMAR!$K$8</f>
+        <v>0.39996458950406311</v>
       </c>
       <c r="G11" s="1">
-        <f>[1]INZERILLI!$K$9</f>
-        <v>3.6214061674180802</v>
+        <f>[1]JAMAR!$K$9</f>
+        <v>0.50891556989622</v>
       </c>
       <c r="H11" s="1">
-        <f>[1]INZERILLI!$K$10</f>
-        <v>3.6867470765089894</v>
-      </c>
-      <c r="I11" s="1"/>
+        <f>[1]JAMAR!$K$10</f>
+        <v>0.31933223656288667</v>
+      </c>
+      <c r="I11" s="1">
+        <f>[1]JAMAR!$K$11</f>
+        <v>0.4440147762454264</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -4568,37 +4674,40 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>[1]JAMAR!$F$2</f>
+        <f>[1]JAMART!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C12" s="1">
-        <f>[1]JAMAR!$K$5</f>
-        <v>0.45900824029771398</v>
+        <f>[1]JAMART!$K$5</f>
+        <v>0.16571660685805426</v>
       </c>
       <c r="D12" s="1">
-        <f>[1]JAMAR!$K$6</f>
-        <v>0.50275824029771399</v>
+        <f>[1]JAMART!$K$6</f>
+        <v>0.12682771796916537</v>
       </c>
       <c r="E12" s="1">
-        <f>[1]JAMAR!$K$7</f>
-        <v>0.83470268474215836</v>
+        <f>[1]JAMART!$K$7</f>
+        <v>0.23885549574694315</v>
       </c>
       <c r="F12" s="1">
-        <f>[1]JAMAR!$K$8</f>
-        <v>0.39996458950406311</v>
+        <f>[1]JAMART!$K$8</f>
+        <v>-5.9120694729247303E-2</v>
       </c>
       <c r="G12" s="1">
-        <f>[1]JAMAR!$K$9</f>
-        <v>0.50891556989622</v>
+        <f>[1]JAMART!$K$9</f>
+        <v>-0.14800794963120809</v>
       </c>
       <c r="H12" s="1">
-        <f>[1]JAMAR!$K$10</f>
-        <v>0.29578678201743214</v>
-      </c>
-      <c r="I12" s="1"/>
+        <f>[1]JAMART!$K$10</f>
+        <v>-0.55687158599484443</v>
+      </c>
+      <c r="I12" s="1">
+        <f>[1]JAMART!$K$11</f>
+        <v>-0.44929222091547927</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -4607,37 +4716,40 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="str">
-        <f>[1]JAMART!$F$2</f>
-        <v xml:space="preserve"> </v>
+        <v>29</v>
+      </c>
+      <c r="B13" s="1">
+        <f>[1]KINIF!$F$2</f>
+        <v>0.38935606060606043</v>
       </c>
       <c r="C13" s="1">
-        <f>[1]JAMART!$K$5</f>
-        <v>0.16571660685805426</v>
+        <f>[1]KINIF!$K$5</f>
+        <v>1.7435227272727272</v>
       </c>
       <c r="D13" s="1">
-        <f>[1]JAMART!$K$6</f>
-        <v>0.12682771796916537</v>
+        <f>[1]KINIF!$K$6</f>
+        <v>1.8185227272727271</v>
       </c>
       <c r="E13" s="1">
-        <f>[1]JAMART!$K$7</f>
-        <v>0.23885549574694315</v>
+        <f>[1]KINIF!$K$7</f>
+        <v>1.8101893939393938</v>
       </c>
       <c r="F13" s="1">
-        <f>[1]JAMART!$K$8</f>
-        <v>-5.9120694729247303E-2</v>
+        <f>[1]KINIF!$K$8</f>
+        <v>1.9601893939393937</v>
       </c>
       <c r="G13" s="1">
-        <f>[1]JAMART!$K$9</f>
-        <v>-0.14800794963120809</v>
+        <f>[1]KINIF!$K$9</f>
+        <v>1.9427302436125962</v>
       </c>
       <c r="H13" s="1">
-        <f>[1]JAMART!$K$10</f>
-        <v>-0.68048269710595555</v>
-      </c>
-      <c r="I13" s="1"/>
+        <f>[1]KINIF!$K$10</f>
+        <v>2.1204575163398687</v>
+      </c>
+      <c r="I13" s="1">
+        <f>[1]KINIF!$K$11</f>
+        <v>1.6128186274509797</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -4646,37 +4758,40 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="1">
-        <f>[1]KINIF!$F$2</f>
-        <v>1.0969949494949494</v>
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>[1]LABBE!$F$2</f>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C14" s="1">
-        <f>[1]KINIF!$K$5</f>
-        <v>1.7435227272727272</v>
+        <f>[1]LABBE!$K$5</f>
+        <v>0.45000000000000007</v>
       </c>
       <c r="D14" s="1">
-        <f>[1]KINIF!$K$6</f>
-        <v>1.8185227272727271</v>
+        <f>[1]LABBE!$K$6</f>
+        <v>0.2680555555555556</v>
       </c>
       <c r="E14" s="1">
-        <f>[1]KINIF!$K$7</f>
-        <v>1.8101893939393938</v>
+        <f>[1]LABBE!$K$7</f>
+        <v>0.30972222222222223</v>
       </c>
       <c r="F14" s="1">
-        <f>[1]KINIF!$K$8</f>
-        <v>1.9601893939393937</v>
+        <f>[1]LABBE!$K$8</f>
+        <v>0.24305555555555558</v>
       </c>
       <c r="G14" s="1">
-        <f>[1]KINIF!$K$9</f>
-        <v>1.9427302436125962</v>
+        <f>[1]LABBE!$K$9</f>
+        <v>0.28472222222222221</v>
       </c>
       <c r="H14" s="1">
-        <f>[1]KINIF!$K$10</f>
-        <v>2.1204575163398687</v>
-      </c>
-      <c r="I14" s="1"/>
+        <f>[1]LABBE!$K$10</f>
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="I14" s="1">
+        <f>[1]LABBE!$K$11</f>
+        <v>0.33640873015873018</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4685,37 +4800,40 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>[1]LABBE!$F$2</f>
+        <f>[1]LAMBERT!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C15" s="1">
-        <f>[1]LABBE!$K$5</f>
-        <v>0.45000000000000007</v>
+        <f>[1]LAMBERT!$K$5</f>
+        <v>0.54502952869657695</v>
       </c>
       <c r="D15" s="1">
-        <f>[1]LABBE!$K$6</f>
-        <v>0.2680555555555556</v>
+        <f>[1]LAMBERT!$K$6</f>
+        <v>0.37766841758546582</v>
       </c>
       <c r="E15" s="1">
-        <f>[1]LABBE!$K$7</f>
-        <v>0.30972222222222223</v>
+        <f>[1]LAMBERT!$K$7</f>
+        <v>1.2318350842521326</v>
       </c>
       <c r="F15" s="1">
-        <f>[1]LABBE!$K$8</f>
-        <v>0.24305555555555558</v>
+        <f>[1]LAMBERT!$K$8</f>
+        <v>1.2690374652045135</v>
       </c>
       <c r="G15" s="1">
-        <f>[1]LABBE!$K$9</f>
-        <v>0.28472222222222221</v>
+        <f>[1]LAMBERT!$K$9</f>
+        <v>1.362093020760069</v>
       </c>
       <c r="H15" s="1">
-        <f>[1]LABBE!$K$10</f>
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="I15" s="1"/>
+        <f>[1]LAMBERT!$K$10</f>
+        <v>1.2565374652045134</v>
+      </c>
+      <c r="I15" s="1">
+        <f>[1]LAMBERT!$K$11</f>
+        <v>1.4433430207600688</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4724,37 +4842,40 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>[1]LAMBERT!$F$2</f>
+        <f>[1]LEMAITRE!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C16" s="1">
-        <f>[1]LAMBERT!$K$5</f>
-        <v>0.53252952869657688</v>
+        <f>[1]LEMAITRE!$K$5</f>
+        <v>0.31578282828282833</v>
       </c>
       <c r="D16" s="1">
-        <f>[1]LAMBERT!$K$6</f>
-        <v>0.15544619536324361</v>
+        <f>[1]LEMAITRE!$K$6</f>
+        <v>0.28244949494949501</v>
       </c>
       <c r="E16" s="1">
-        <f>[1]LAMBERT!$K$7</f>
-        <v>1.0096128620299103</v>
+        <f>[1]LEMAITRE!$K$7</f>
+        <v>0.67342171717171728</v>
       </c>
       <c r="F16" s="1">
-        <f>[1]LAMBERT!$K$8</f>
-        <v>1.0468152429822912</v>
+        <f>[1]LEMAITRE!$K$8</f>
+        <v>0.43592171717171729</v>
       </c>
       <c r="G16" s="1">
-        <f>[1]LAMBERT!$K$9</f>
-        <v>1.1256060926554938</v>
+        <f>[1]LEMAITRE!$K$9</f>
+        <v>0.43592171717171729</v>
       </c>
       <c r="H16" s="1">
-        <f>[1]LAMBERT!$K$10</f>
-        <v>0.8603283148777161</v>
-      </c>
-      <c r="I16" s="1"/>
+        <f>[1]LEMAITRE!$K$10</f>
+        <v>0.41508838383838398</v>
+      </c>
+      <c r="I16" s="1">
+        <f>[1]LEMAITRE!$K$11</f>
+        <v>0.35883838383838396</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -4763,37 +4884,40 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>[1]LEMAITRE!$F$2</f>
+        <f>[1]LIEGEOIS!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C17" s="1">
-        <f>[1]LEMAITRE!$K$5</f>
-        <v>0.31578282828282833</v>
+        <f>[1]LIEGEOIS!$K$5</f>
+        <v>1.5277777777778029E-2</v>
       </c>
       <c r="D17" s="1">
-        <f>[1]LEMAITRE!$K$6</f>
-        <v>0.28244949494949501</v>
+        <f>[1]LIEGEOIS!$K$6</f>
+        <v>0.12361111111111137</v>
       </c>
       <c r="E17" s="1">
-        <f>[1]LEMAITRE!$K$7</f>
-        <v>0.67342171717171728</v>
+        <f>[1]LIEGEOIS!$K$7</f>
+        <v>0.19469696969696995</v>
       </c>
       <c r="F17" s="1">
-        <f>[1]LEMAITRE!$K$8</f>
-        <v>0.43592171717171729</v>
+        <f>[1]LIEGEOIS!$K$8</f>
+        <v>0.29678030303030328</v>
       </c>
       <c r="G17" s="1">
-        <f>[1]LEMAITRE!$K$9</f>
-        <v>0.43592171717171729</v>
+        <f>[1]LIEGEOIS!$K$9</f>
+        <v>0.42178030303030328</v>
       </c>
       <c r="H17" s="1">
-        <f>[1]LEMAITRE!$K$10</f>
-        <v>0.41508838383838398</v>
-      </c>
-      <c r="I17" s="1"/>
+        <f>[1]LIEGEOIS!$K$10</f>
+        <v>0.49416035353535381</v>
+      </c>
+      <c r="I17" s="1">
+        <f>[1]LIEGEOIS!$K$11</f>
+        <v>0.5219381313131316</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -4802,37 +4926,40 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>[1]LIEGEOIS!$F$2</f>
+        <f>[1]MOSCATO!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C18" s="1">
-        <f>[1]LIEGEOIS!$K$5</f>
-        <v>1.5277777777778029E-2</v>
+        <f>[1]MOSCATO!$K$5</f>
+        <v>0.65694444444444478</v>
       </c>
       <c r="D18" s="1">
-        <f>[1]LIEGEOIS!$K$6</f>
-        <v>0.11736111111111136</v>
+        <f>[1]MOSCATO!$K$6</f>
+        <v>0.68750000000000033</v>
       </c>
       <c r="E18" s="1">
-        <f>[1]LIEGEOIS!$K$7</f>
-        <v>0.17651515151515176</v>
+        <f>[1]MOSCATO!$K$7</f>
+        <v>1.6868055555555559</v>
       </c>
       <c r="F18" s="1">
-        <f>[1]LIEGEOIS!$K$8</f>
-        <v>0.2785984848484851</v>
+        <f>[1]MOSCATO!$K$8</f>
+        <v>2.0965277777777782</v>
       </c>
       <c r="G18" s="1">
-        <f>[1]LIEGEOIS!$K$9</f>
-        <v>0.4035984848484851</v>
+        <f>[1]MOSCATO!$K$9</f>
+        <v>1.7548611111111114</v>
       </c>
       <c r="H18" s="1">
-        <f>[1]LIEGEOIS!$K$10</f>
-        <v>0.47029671717171739</v>
-      </c>
-      <c r="I18" s="1"/>
+        <f>[1]MOSCATO!$K$10</f>
+        <v>1.8895833333333336</v>
+      </c>
+      <c r="I18" s="1">
+        <f>[1]MOSCATO!$K$11</f>
+        <v>2.0402777777777779</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -4841,37 +4968,40 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>[1]MOSCATO!$F$2</f>
+        <f>[1]NEZER!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C19" s="1">
-        <f>[1]MOSCATO!$K$5</f>
-        <v>0.65694444444444478</v>
+        <f>[1]NEZER!$K$5</f>
+        <v>2.0516388888888888</v>
       </c>
       <c r="D19" s="1">
-        <f>[1]MOSCATO!$K$6</f>
-        <v>0.68750000000000033</v>
+        <f>[1]NEZER!$K$6</f>
+        <v>1.955111111111111</v>
       </c>
       <c r="E19" s="1">
-        <f>[1]MOSCATO!$K$7</f>
-        <v>1.6868055555555559</v>
+        <f>[1]NEZER!$K$7</f>
+        <v>2.7551111111111113</v>
       </c>
       <c r="F19" s="1">
-        <f>[1]MOSCATO!$K$8</f>
-        <v>2.0965277777777782</v>
+        <f>[1]NEZER!$K$8</f>
+        <v>2.5606666666666671</v>
       </c>
       <c r="G19" s="1">
-        <f>[1]MOSCATO!$K$9</f>
-        <v>1.7548611111111114</v>
+        <f>[1]NEZER!$K$9</f>
+        <v>2.7606666666666673</v>
       </c>
       <c r="H19" s="1">
-        <f>[1]MOSCATO!$K$10</f>
-        <v>1.8787878787878791</v>
-      </c>
-      <c r="I19" s="1"/>
+        <f>[1]NEZER!$K$10</f>
+        <v>2.283583333333334</v>
+      </c>
+      <c r="I19" s="1">
+        <f>[1]NEZER!$K$11</f>
+        <v>1.8676111111111118</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -4880,37 +5010,40 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1">
-        <f>[1]NEZER!$F$2</f>
-        <v>7.8888888888886122E-3</v>
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <f>[1]PESESSE!$F$2</f>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C20" s="1">
-        <f>[1]NEZER!$K$5</f>
-        <v>2.0516388888888888</v>
+        <f>[1]PESESSE!$K$5</f>
+        <v>0.52355545154057737</v>
       </c>
       <c r="D20" s="1">
-        <f>[1]NEZER!$K$6</f>
-        <v>1.955111111111111</v>
+        <f>[1]PESESSE!$K$6</f>
+        <v>0.40549989598502179</v>
       </c>
       <c r="E20" s="1">
-        <f>[1]NEZER!$K$7</f>
-        <v>2.7551111111111113</v>
+        <f>[1]PESESSE!$K$7</f>
+        <v>0.59163625962138544</v>
       </c>
       <c r="F20" s="1">
-        <f>[1]NEZER!$K$8</f>
-        <v>2.5606666666666671</v>
+        <f>[1]PESESSE!$K$8</f>
+        <v>0.44086245009757596</v>
       </c>
       <c r="G20" s="1">
-        <f>[1]NEZER!$K$9</f>
-        <v>2.7606666666666673</v>
+        <f>[1]PESESSE!$K$9</f>
+        <v>0.28481669846358904</v>
       </c>
       <c r="H20" s="1">
-        <f>[1]NEZER!$K$10</f>
-        <v>2.283583333333334</v>
-      </c>
-      <c r="I20" s="1"/>
+        <f>[1]PESESSE!$K$10</f>
+        <v>0.35779649644338701</v>
+      </c>
+      <c r="I20" s="1">
+        <f>[1]PESESSE!$K$11</f>
+        <v>0.40868935358624414</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4919,37 +5052,40 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>[1]PESESSE!$F$2</f>
+        <f>[1]SEGHIAR!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C21" s="1">
-        <f>[1]PESESSE!$K$5</f>
-        <v>0.52355545154057737</v>
+        <f>[1]SEGHIAR!$K$5</f>
+        <v>0.35624999999999996</v>
       </c>
       <c r="D21" s="1">
-        <f>[1]PESESSE!$K$6</f>
-        <v>0.40549989598502179</v>
+        <f>[1]SEGHIAR!$K$6</f>
+        <v>0.37222222222222218</v>
       </c>
       <c r="E21" s="1">
-        <f>[1]PESESSE!$K$7</f>
-        <v>0.59163625962138544</v>
+        <f>[1]SEGHIAR!$K$7</f>
+        <v>0.31755050505050497</v>
       </c>
       <c r="F21" s="1">
-        <f>[1]PESESSE!$K$8</f>
-        <v>0.44086245009757596</v>
+        <f>[1]SEGHIAR!$K$8</f>
+        <v>0.2203679653679653</v>
       </c>
       <c r="G21" s="1">
-        <f>[1]PESESSE!$K$9</f>
-        <v>0.28481669846358904</v>
+        <f>[1]SEGHIAR!$K$9</f>
+        <v>0.2203679653679653</v>
       </c>
       <c r="H21" s="1">
-        <f>[1]PESESSE!$K$10</f>
-        <v>0.35779649644338701</v>
-      </c>
-      <c r="I21" s="1"/>
+        <f>[1]SEGHIAR!$K$10</f>
+        <v>0.2203679653679653</v>
+      </c>
+      <c r="I21" s="1">
+        <f>[1]SEGHIAR!$K$11</f>
+        <v>0.2203679653679653</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -4958,37 +5094,40 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>[1]SEGHIAR!$F$2</f>
+        <f>[1]SUSAM!$F$2</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C22" s="1">
-        <f>[1]SEGHIAR!$K$5</f>
-        <v>0.35624999999999996</v>
+        <f>[1]SUSAM!$K$5</f>
+        <v>3.4743055555555555</v>
       </c>
       <c r="D22" s="1">
-        <f>[1]SEGHIAR!$K$6</f>
-        <v>0.37222222222222218</v>
+        <f>[1]SUSAM!$K$6</f>
+        <v>1.8340277777777778</v>
       </c>
       <c r="E22" s="1">
-        <f>[1]SEGHIAR!$K$7</f>
-        <v>0.31755050505050497</v>
+        <f>[1]SUSAM!$K$7</f>
+        <v>1.7347222222222223</v>
       </c>
       <c r="F22" s="1">
-        <f>[1]SEGHIAR!$K$8</f>
-        <v>0.2203679653679653</v>
+        <f>[1]SUSAM!$K$8</f>
+        <v>2.0229166666666667</v>
       </c>
       <c r="G22" s="1">
-        <f>[1]SEGHIAR!$K$9</f>
-        <v>0.2203679653679653</v>
+        <f>[1]SUSAM!$K$9</f>
+        <v>2.1479166666666667</v>
       </c>
       <c r="H22" s="1">
-        <f>[1]SEGHIAR!$K$10</f>
-        <v>0.2203679653679653</v>
-      </c>
-      <c r="I22" s="1"/>
+        <f>[1]SUSAM!$K$10</f>
+        <v>2.3562500000000002</v>
+      </c>
+      <c r="I22" s="1">
+        <f>[1]SUSAM!$K$11</f>
+        <v>1.6562500000000002</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -4997,87 +5136,51 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <f>[1]SUSAM!$F$2</f>
-        <v>0.65000000000000036</v>
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <f>[1]TIBEAU!$F$2</f>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C23" s="1">
-        <f>[1]SUSAM!$K$5</f>
-        <v>3.4743055555555555</v>
+        <f>[1]TIBEAU!$K$5</f>
+        <v>0.39374999999999993</v>
       </c>
       <c r="D23" s="1">
-        <f>[1]SUSAM!$K$6</f>
-        <v>1.8340277777777778</v>
+        <f>[1]TIBEAU!$K$6</f>
+        <v>0.5659722222222221</v>
       </c>
       <c r="E23" s="1">
-        <f>[1]SUSAM!$K$7</f>
-        <v>1.7347222222222223</v>
+        <f>[1]TIBEAU!$K$7</f>
+        <v>0.43446969696969684</v>
       </c>
       <c r="F23" s="1">
-        <f>[1]SUSAM!$K$8</f>
-        <v>2.0229166666666667</v>
+        <f>[1]TIBEAU!$K$8</f>
+        <v>0.14141414141414133</v>
       </c>
       <c r="G23" s="1">
-        <f>[1]SUSAM!$K$9</f>
-        <v>2.1479166666666667</v>
+        <f>[1]TIBEAU!$K$9</f>
+        <v>-0.10511363636363646</v>
       </c>
       <c r="H23" s="1">
-        <f>[1]SUSAM!$K$10</f>
-        <v>2.2972222222222221</v>
-      </c>
-      <c r="I23" s="1"/>
+        <f>[1]TIBEAU!$K$10</f>
+        <v>-3.0303030303031608E-3</v>
+      </c>
+      <c r="I23" s="1">
+        <f>[1]TIBEAU!$K$11</f>
+        <v>-7.1969696969698127E-3</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="str">
-        <f>[1]TIBEAU!$F$2</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C24" s="1">
-        <f>[1]TIBEAU!$K$5</f>
-        <v>0.39374999999999993</v>
-      </c>
-      <c r="D24" s="1">
-        <f>[1]TIBEAU!$K$6</f>
-        <v>0.5659722222222221</v>
-      </c>
-      <c r="E24" s="1">
-        <f>[1]TIBEAU!$K$7</f>
-        <v>0.43446969696969684</v>
-      </c>
-      <c r="F24" s="1">
-        <f>[1]TIBEAU!$K$8</f>
-        <v>0.14141414141414133</v>
-      </c>
-      <c r="G24" s="1">
-        <f>[1]TIBEAU!$K$9</f>
-        <v>-0.10511363636363646</v>
-      </c>
-      <c r="H24" s="1">
-        <f>[1]TIBEAU!$K$10</f>
-        <v>-3.0303030303031608E-3</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C2 C18:C22 C3:C17 C23:C24" calculatedColumn="1"/>
+    <ignoredError sqref="C2 C17:C21 C3:C6 C22:C23 C7:C16" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5086,6 +5189,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a6b1418315c503125b81deceb3e14f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db3d71b0-92fa-400b-b303-110676c7e1a6" xmlns:ns3="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b9cfce4172cb86f233e713e45f29f51c" ns2:_="" ns3:_="">
     <xsd:import namespace="db3d71b0-92fa-400b-b303-110676c7e1a6"/>
@@ -5296,26 +5418,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A27A95-3717-46C0-8F53-2FF09BECAD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5332,22 +5453,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>